--- a/Documents/Product Catalog/Home/Tv Cabinet.xlsx
+++ b/Documents/Product Catalog/Home/Tv Cabinet.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PENDRIVE\Tv Cabinet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\By Raj\Talukder Furniture\Documents\Product Catalog\Home\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EABB956-4108-4CDA-A8AE-2DEE3DF734CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="3375" yWindow="3375" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tv Cabinet " sheetId="10" r:id="rId1"/>
@@ -17,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Tv Cabinet '!$A$1:$Q$6</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
   <si>
     <t>Home Furniture Specifications</t>
   </si>
@@ -165,11 +179,17 @@
   <si>
     <t>Organizer/TV Cabinets</t>
   </si>
+  <si>
+    <t>কদম্বরী TV Cabinet</t>
+  </si>
+  <si>
+    <t>বিপরীত TV Cabinet</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="9">
     <font>
       <sz val="10"/>
@@ -503,13 +523,22 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -528,15 +557,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -736,7 +756,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="16"/>
       <tableStyleElement type="headerRow" dxfId="15"/>
       <tableStyleElement type="totalRow" dxfId="14"/>
@@ -745,7 +765,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="11"/>
       <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="headerRow" dxfId="9"/>
       <tableStyleElement type="totalRow" dxfId="8"/>
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
@@ -784,7 +804,7 @@
         <xdr:cNvPr id="115" name="image103.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -829,7 +849,7 @@
         <xdr:cNvPr id="218" name="image201.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DC000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DC000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -874,7 +894,7 @@
         <xdr:cNvPr id="257" name="image240.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -924,7 +944,7 @@
         <xdr:cNvPr id="277" name="image260.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -974,7 +994,7 @@
         <xdr:cNvPr id="278" name="image261.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1019,7 +1039,7 @@
         <xdr:cNvPr id="326" name="image1.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1303,7 +1323,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AT74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
@@ -1328,49 +1348,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
     </row>
     <row r="2" spans="1:46" ht="39.950000000000003" customHeight="1">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
     </row>
     <row r="3" spans="1:46" ht="50.1" customHeight="1">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="31" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="25" t="s">
@@ -1379,28 +1399,28 @@
       <c r="C3" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F3" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="34"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="28"/>
       <c r="I3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="30" t="s">
+      <c r="J3" s="33" t="s">
         <v>8</v>
       </c>
       <c r="K3" s="25" t="s">
         <v>9</v>
       </c>
       <c r="L3" s="25"/>
-      <c r="M3" s="32"/>
+      <c r="M3" s="26"/>
       <c r="N3" s="25" t="s">
         <v>10</v>
       </c>
@@ -1443,11 +1463,11 @@
       <c r="AT3" s="4"/>
     </row>
     <row r="4" spans="1:46" ht="33.200000000000003" customHeight="1">
-      <c r="A4" s="29"/>
+      <c r="A4" s="32"/>
       <c r="B4" s="25"/>
       <c r="C4" s="25"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
       <c r="F4" s="24" t="s">
         <v>12</v>
       </c>
@@ -1458,7 +1478,7 @@
         <v>32</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="J4" s="31"/>
+      <c r="J4" s="34"/>
       <c r="K4" s="5" t="s">
         <v>14</v>
       </c>
@@ -1509,7 +1529,7 @@
         <v>35</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="9" t="s">
@@ -1589,7 +1609,7 @@
         <v>34</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="7" t="s">
@@ -4658,11 +4678,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
@@ -4673,6 +4688,11 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="10" orientation="portrait" r:id="rId1"/>
